--- a/Design-Files/Project Outputs for Francisco Gimenez/Francisco Gimenez.xlsx
+++ b/Design-Files/Project Outputs for Francisco Gimenez/Francisco Gimenez.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="236">
   <si>
     <t>Comment</t>
   </si>
@@ -200,13 +200,169 @@
     <t>Diodes</t>
   </si>
   <si>
+    <t>SS54B-HF</t>
+  </si>
+  <si>
+    <t>DIODE SCHOTTKY 5A 40V SMB</t>
+  </si>
+  <si>
+    <t>D6</t>
+  </si>
+  <si>
+    <t>SMB</t>
+  </si>
+  <si>
+    <t>Comchip</t>
+  </si>
+  <si>
+    <t>HDR_F_1X7</t>
+  </si>
+  <si>
+    <t>7 POS 2.54mm female header</t>
+  </si>
+  <si>
+    <t>J1, J15</t>
+  </si>
+  <si>
+    <t>HDR_F_1X4</t>
+  </si>
+  <si>
+    <t>4 POS 2.54mm female header</t>
+  </si>
+  <si>
+    <t>J2</t>
+  </si>
+  <si>
+    <t>B2B-XH-A(LF)(SN)</t>
+  </si>
+  <si>
+    <t>Conn Shrouded Header (4 Sides) HDR 2 POS 2.5mm Solder ST Thru-Hole Box</t>
+  </si>
+  <si>
+    <t>J3, J24, J25, J28, J29</t>
+  </si>
+  <si>
+    <t>JST</t>
+  </si>
+  <si>
+    <t>B4B-XH-A(LF)(SN)</t>
+  </si>
+  <si>
+    <t>CONN HEADER VERT 4POS 2.5MM</t>
+  </si>
+  <si>
+    <t>J4</t>
+  </si>
+  <si>
+    <t>HDR_F_1X3</t>
+  </si>
+  <si>
+    <t>3 POS 2.54mm female header</t>
+  </si>
+  <si>
+    <t>J10, J11, J12, J13, J20</t>
+  </si>
+  <si>
+    <t>B7B-XH-A(LF)(SN)</t>
+  </si>
+  <si>
+    <t>CONN HEADER VERT 7POS 2.5MM</t>
+  </si>
+  <si>
+    <t>J14</t>
+  </si>
+  <si>
+    <t>2305018-2</t>
+  </si>
+  <si>
+    <t>CONN RCP USB3.1 TYPEC 24P SMD RA</t>
+  </si>
+  <si>
+    <t>J16</t>
+  </si>
+  <si>
+    <t>B3B-XH-A(LF)(SN)</t>
+  </si>
+  <si>
+    <t>CONN HEADER VERT 3POS 2.5MM</t>
+  </si>
+  <si>
+    <t>J30</t>
+  </si>
+  <si>
+    <t>3.3uH</t>
+  </si>
+  <si>
+    <t>FIXED IND 3.3UH 8A 11.8 MOHM SMD</t>
+  </si>
+  <si>
+    <t>L1, L3</t>
+  </si>
+  <si>
+    <t>74437368033</t>
+  </si>
+  <si>
+    <t>Wurth Electronics</t>
+  </si>
+  <si>
+    <t>10uH</t>
+  </si>
+  <si>
+    <t>FIXED IND 10UH 2.5A 43.7 MOHM</t>
+  </si>
+  <si>
+    <t>L2</t>
+  </si>
+  <si>
+    <t>SLF10145T-100M2R5-PF</t>
+  </si>
+  <si>
+    <t>TDK</t>
+  </si>
+  <si>
+    <t>LTST-C170KSKT</t>
+  </si>
+  <si>
+    <t>Yellow 2 x 1.25 x 1.1 mm 130° Water Clear 112 mcd 1.8 V LED Surface Mount</t>
+  </si>
+  <si>
+    <t>LED1</t>
+  </si>
+  <si>
+    <t>Vishay Lite-On</t>
+  </si>
+  <si>
+    <t>17-21/BHC-XL2M2TY/3T</t>
+  </si>
+  <si>
+    <t>LED BLUE 0805 SMD</t>
+  </si>
+  <si>
+    <t>LED2</t>
+  </si>
+  <si>
+    <t>Everlight Elec</t>
+  </si>
+  <si>
+    <t>LTST-C171KGKT</t>
+  </si>
+  <si>
+    <t>LED GREEN 574nm 2-Pin Chip 0805 SMD</t>
+  </si>
+  <si>
+    <t>LED3</t>
+  </si>
+  <si>
+    <t>LED 0805</t>
+  </si>
+  <si>
     <t>XZVG68W-2</t>
   </si>
   <si>
     <t>LED GREEN CLEAR CHIP SMD</t>
   </si>
   <si>
-    <t>D4, D5</t>
+    <t>LED4, LED5</t>
   </si>
   <si>
     <t>LED 0402</t>
@@ -215,168 +371,6 @@
     <t>SunLED</t>
   </si>
   <si>
-    <t>SS54B-HF</t>
-  </si>
-  <si>
-    <t>DIODE SCHOTTKY 5A 40V SMB</t>
-  </si>
-  <si>
-    <t>D6</t>
-  </si>
-  <si>
-    <t>SMB</t>
-  </si>
-  <si>
-    <t>Comchip</t>
-  </si>
-  <si>
-    <t>RFID Carousel</t>
-  </si>
-  <si>
-    <t>CONN HEADER VERT 7POS 2.5MM</t>
-  </si>
-  <si>
-    <t>J1</t>
-  </si>
-  <si>
-    <t>B7B-XH-A(LF)(SN)</t>
-  </si>
-  <si>
-    <t>JST</t>
-  </si>
-  <si>
-    <t>Weight Sensor</t>
-  </si>
-  <si>
-    <t>CONN HEADER VERT 4POS 2.5MM</t>
-  </si>
-  <si>
-    <t>J2</t>
-  </si>
-  <si>
-    <t>B4B-XH-A(LF)(SN)</t>
-  </si>
-  <si>
-    <t>B2B-XH-A(LF)(SN)</t>
-  </si>
-  <si>
-    <t>Conn Shrouded Header (4 Sides) HDR 2 POS 2.5mm Solder ST Thru-Hole Box</t>
-  </si>
-  <si>
-    <t>J3, J24, J25, J28, J29</t>
-  </si>
-  <si>
-    <t>WS2812B</t>
-  </si>
-  <si>
-    <t>CONN HEADER VERT 3POS 2.5MM</t>
-  </si>
-  <si>
-    <t>J4, J10, J11, J20</t>
-  </si>
-  <si>
-    <t>B3B-XH-A(LF)(SN)</t>
-  </si>
-  <si>
-    <t>Optical Sensor</t>
-  </si>
-  <si>
-    <t>J13</t>
-  </si>
-  <si>
-    <t>RFID Tablet</t>
-  </si>
-  <si>
-    <t>J14</t>
-  </si>
-  <si>
-    <t>RFID Tray</t>
-  </si>
-  <si>
-    <t>J15</t>
-  </si>
-  <si>
-    <t>2305018-2</t>
-  </si>
-  <si>
-    <t>CONN RCP USB3.1 TYPEC 24P SMD RA</t>
-  </si>
-  <si>
-    <t>J16</t>
-  </si>
-  <si>
-    <t>J17</t>
-  </si>
-  <si>
-    <t>J30</t>
-  </si>
-  <si>
-    <t>3.3uH</t>
-  </si>
-  <si>
-    <t>FIXED IND 3.3UH 8A 11.8 MOHM SMD</t>
-  </si>
-  <si>
-    <t>L1, L3</t>
-  </si>
-  <si>
-    <t>74437368033</t>
-  </si>
-  <si>
-    <t>Wurth Electronics</t>
-  </si>
-  <si>
-    <t>10uH</t>
-  </si>
-  <si>
-    <t>FIXED IND 10UH 2.5A 43.7 MOHM</t>
-  </si>
-  <si>
-    <t>L2</t>
-  </si>
-  <si>
-    <t>SLF10145T-100M2R5-PF</t>
-  </si>
-  <si>
-    <t>TDK</t>
-  </si>
-  <si>
-    <t>LTST-C170KSKT</t>
-  </si>
-  <si>
-    <t>Yellow 2 x 1.25 x 1.1 mm 130° Water Clear 112 mcd 1.8 V LED Surface Mount</t>
-  </si>
-  <si>
-    <t>LED1</t>
-  </si>
-  <si>
-    <t>Vishay Lite-On</t>
-  </si>
-  <si>
-    <t>17-21/BHC-XL2M2TY/3T</t>
-  </si>
-  <si>
-    <t>LED BLUE 0805 SMD</t>
-  </si>
-  <si>
-    <t>LED2</t>
-  </si>
-  <si>
-    <t>Everlight Elec</t>
-  </si>
-  <si>
-    <t>LTST-C171KGKT</t>
-  </si>
-  <si>
-    <t>LED GREEN 574nm 2-Pin Chip 0805 SMD</t>
-  </si>
-  <si>
-    <t>LED3</t>
-  </si>
-  <si>
-    <t>LED 0805</t>
-  </si>
-  <si>
     <t>Test Point</t>
   </si>
   <si>
@@ -704,7 +698,7 @@
     <t>IC BUF NON-INVERT 5.5V SOT23-5</t>
   </si>
   <si>
-    <t>U7, U8, U19, U?</t>
+    <t>U7, U8, U10, U19</t>
   </si>
   <si>
     <t>SOT-23-5</t>
@@ -747,7 +741,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -755,15 +749,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -773,12 +760,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD3D3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -810,7 +791,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -820,12 +801,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1111,7 +1086,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="16.5703125" customWidth="1"/>
@@ -1154,7 +1129,7 @@
       <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="3" t="s">
@@ -1180,7 +1155,7 @@
       <c r="B3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D3" s="3" t="s">
@@ -1206,7 +1181,7 @@
       <c r="B4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -1232,7 +1207,7 @@
       <c r="B5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D5" s="3" t="s">
@@ -1258,7 +1233,7 @@
       <c r="B6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="D6" s="3" t="s">
@@ -1284,7 +1259,7 @@
       <c r="B7" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D7" s="3" t="s">
@@ -1310,7 +1285,7 @@
       <c r="B8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="3" t="s">
         <v>40</v>
       </c>
       <c r="D8" s="3" t="s">
@@ -1336,7 +1311,7 @@
       <c r="B9" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D9" s="3" t="s">
@@ -1358,7 +1333,7 @@
       <c r="B10" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D10" s="3" t="s">
@@ -1384,7 +1359,7 @@
       <c r="B11" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="3" t="s">
         <v>54</v>
       </c>
       <c r="D11" s="3" t="s">
@@ -1410,7 +1385,7 @@
       <c r="B12" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="3" t="s">
         <v>59</v>
       </c>
       <c r="D12" s="3" t="s">
@@ -1423,7 +1398,7 @@
         <v>57</v>
       </c>
       <c r="G12" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>61</v>
@@ -1436,147 +1411,135 @@
       <c r="B13" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="3" t="s">
         <v>64</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>62</v>
-      </c>
+      <c r="F13" s="4"/>
       <c r="G13" s="4">
-        <v>1</v>
-      </c>
-      <c r="H13" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H13" s="4"/>
+    </row>
+    <row r="14" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="D14" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4"/>
+    </row>
+    <row r="15" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="B15" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="G14" s="4">
-        <v>1</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="D15" s="3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="G15" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>76</v>
+    <row r="16" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>72</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="G16" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4">
+        <v>5</v>
+      </c>
+      <c r="H17" s="4"/>
+    </row>
+    <row r="18" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="C18" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="G17" s="4">
-        <v>4</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>82</v>
+      <c r="D18" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>78</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G18" s="4">
         <v>1</v>
@@ -1587,48 +1550,44 @@
     </row>
     <row r="19" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>70</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="F19" s="4"/>
       <c r="G19" s="4">
         <v>1</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>71</v>
-      </c>
+      <c r="H19" s="4"/>
     </row>
     <row r="20" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="G20" s="4">
         <v>1</v>
@@ -1639,480 +1598,484 @@
     </row>
     <row r="21" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="E21" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G21" s="4">
+        <v>2</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4">
-        <v>1</v>
-      </c>
-      <c r="H21" s="4"/>
-    </row>
-    <row r="22" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C22" s="5" t="s">
+    </row>
+    <row r="22" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>75</v>
+      <c r="B22" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="G22" s="4">
         <v>1</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>82</v>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="G23" s="4">
         <v>1</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>97</v>
-      </c>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F24" s="4"/>
       <c r="G24" s="4">
+        <v>1</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G25" s="4">
+        <v>1</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G26" s="4">
         <v>2</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="G25" s="4">
-        <v>1</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="G26" s="4">
-        <v>1</v>
-      </c>
       <c r="H26" s="3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>108</v>
+      <c r="A27" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>118</v>
       </c>
       <c r="F27" s="4"/>
       <c r="G27" s="4">
-        <v>1</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>111</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="H27" s="4"/>
     </row>
     <row r="28" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>112</v>
+      <c r="A28" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="G28" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>107</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="F29" s="4"/>
+      <c r="A29" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>123</v>
+      </c>
       <c r="G29" s="4">
-        <v>6</v>
-      </c>
-      <c r="H29" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="30" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>121</v>
+      <c r="A30" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>127</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="G30" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>125</v>
+        <v>131</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>136</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="G31" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>129</v>
+      <c r="A32" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>141</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="G32" s="4">
         <v>1</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="B33" s="5" t="s">
+      <c r="A33" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="D33" s="5" t="s">
+      <c r="E33" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G33" s="4">
+        <v>7</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G34" s="4">
+        <v>1</v>
+      </c>
+      <c r="H34" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E33" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="G33" s="4">
-        <v>4</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="G34" s="4">
-        <v>1</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>144</v>
-      </c>
     </row>
     <row r="35" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>148</v>
+      <c r="A35" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>155</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="G35" s="4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A36" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>153</v>
+      <c r="A36" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>160</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G36" s="4">
         <v>1</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>157</v>
+      <c r="A37" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>165</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="G37" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>158</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A38" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>162</v>
+      <c r="A38" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>169</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="G38" s="4">
         <v>1</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>167</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>173</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="G39" s="4">
         <v>1</v>
@@ -2121,443 +2084,391 @@
         <v>23</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="D40" s="5" t="s">
+    <row r="40" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G40" s="4">
+        <v>1</v>
+      </c>
+      <c r="H40" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E40" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="G40" s="4">
-        <v>1</v>
-      </c>
-      <c r="H40" s="3" t="s">
+    </row>
+    <row r="41" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G41" s="4">
+        <v>1</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G42" s="4">
+        <v>1</v>
+      </c>
+      <c r="H42" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="G41" s="4">
-        <v>1</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="G42" s="4">
-        <v>1</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="C43" s="5" t="s">
+    <row r="43" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="G43" s="4">
+        <v>4</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4">
+        <v>1</v>
+      </c>
+      <c r="H44" s="4"/>
+    </row>
+    <row r="45" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="G45" s="4">
+        <v>1</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="G46" s="4">
+        <v>1</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="G47" s="4">
+        <v>1</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="G48" s="4">
+        <v>1</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="G49" s="4">
+        <v>1</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4">
+        <v>1</v>
+      </c>
+      <c r="H50" s="4"/>
+    </row>
+    <row r="51" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G51" s="4">
+        <v>4</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="G52" s="4">
+        <v>1</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="G53" s="4">
+        <v>1</v>
+      </c>
+      <c r="H53" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="D43" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="G43" s="4">
-        <v>1</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="90" x14ac:dyDescent="0.25">
-      <c r="A44" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="G44" s="4">
-        <v>1</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A45" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G45" s="4">
-        <v>4</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="F46" s="4"/>
-      <c r="G46" s="4">
-        <v>1</v>
-      </c>
-      <c r="H46" s="4"/>
-    </row>
-    <row r="47" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A47" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="G47" s="4">
-        <v>1</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A48" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G48" s="4">
-        <v>1</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A49" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="E49" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G49" s="4">
-        <v>1</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A50" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="G50" s="4">
-        <v>1</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A51" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="G51" s="4">
-        <v>1</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A52" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4">
-        <v>1</v>
-      </c>
-      <c r="H52" s="4"/>
-    </row>
-    <row r="53" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A53" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="D53" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="G53" s="4">
-        <v>4</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A54" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>227</v>
+    </row>
+    <row r="54" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>232</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="G54" s="4">
         <v>1</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A55" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="G55" s="4">
-        <v>1</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A56" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="E56" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="G56" s="4">
-        <v>1</v>
-      </c>
-      <c r="H56" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.30555555555555558" right="0.30555555555555558" top="0.30555555555555558" bottom="0.30555555555555558" header="0" footer="0"/>
-  <pageSetup scale="24" orientation="landscape" blackAndWhite="1" r:id="rId1"/>
+  <pageSetup scale="26" orientation="landscape" blackAndWhite="1" r:id="rId1"/>
 </worksheet>
 </file>